--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,82 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>nn_input</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>nn_input</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
     <t>Ibr_from_i_tot</t>
   </si>
   <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
   </si>
   <si>
     <t>cost_tot</t>
   </si>
   <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
     <t>Ibr_to_r_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
+    <t>1.86 (245.00)</t>
   </si>
   <si>
     <t>24164.39 (24469.43 &gt; 1.25%)</t>
   </si>
   <si>
-    <t>1.86 (2.45)</t>
+    <t>1.83 (245.00)</t>
   </si>
   <si>
     <t>24223.81 (24469.43 &gt; 1.00%)</t>
   </si>
   <si>
-    <t>1.83 (2.45)</t>
+    <t>-0.33 (245.00)</t>
   </si>
   <si>
     <t>23284.39 (24469.43 &gt; 4.84%)</t>
   </si>
   <si>
-    <t>-0.33 (2.45)</t>
+    <t>-0.31 (245.00)</t>
   </si>
   <si>
     <t>23941.81 (24469.43 &gt; 2.16%)</t>
-  </si>
-  <si>
-    <t>-0.31 (2.45)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -489,16 +492,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.01297647133469582</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.01297844015061855</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>5.329580744728446E-05</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0001148934825323522</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -506,50 +509,38 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.1062388271093369</v>
+        <v>0.003939139346975322</v>
       </c>
       <c r="C3">
-        <v>0.1062256321310997</v>
+        <v>0.00568355301835495</v>
       </c>
       <c r="D3">
-        <v>0.09499316662549973</v>
+        <v>0.1887047439813614</v>
       </c>
       <c r="E3">
-        <v>0.04188175871968269</v>
+        <v>0.3513489663600922</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.09793540183382518</v>
+        <v>0.001561637036502361</v>
       </c>
       <c r="C5">
-        <v>0.09792175319399953</v>
+        <v>0.001561732147820294</v>
       </c>
       <c r="D5">
-        <v>0.09450215846300125</v>
+        <v>4.623780478141271E-05</v>
       </c>
       <c r="E5">
-        <v>0.04105793312191963</v>
+        <v>0.0001335741690127179</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,16 +548,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.01297650020569563</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.01297846809029579</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>5.329580744728446E-05</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.0001148934825323522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -574,16 +565,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.006729983093325188</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.006729503969950566</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.001301928539760411</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.002461298601701856</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -591,16 +582,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.02442501988871247</v>
+        <v>0.0007623033015988767</v>
       </c>
       <c r="C8">
-        <v>0.02442226940976475</v>
+        <v>0.0007623036508448422</v>
       </c>
       <c r="D8">
-        <v>0.004020011052489281</v>
+        <v>4.537929999059997E-05</v>
       </c>
       <c r="E8">
-        <v>0.01057404559105635</v>
+        <v>0.0001242232538061216</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -608,16 +599,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.006825886711514326</v>
+        <v>0.05889571085572243</v>
       </c>
       <c r="C9">
-        <v>0.00682541339598981</v>
+        <v>0.05889439955353737</v>
       </c>
       <c r="D9">
-        <v>0.001353921135887504</v>
+        <v>0.003857571631669998</v>
       </c>
       <c r="E9">
-        <v>0.002483428455889225</v>
+        <v>0.01070790458470583</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -625,16 +616,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.001561671961098909</v>
+        <v>0.1062386929988861</v>
       </c>
       <c r="C10">
-        <v>0.001561767887324095</v>
+        <v>0.106225498020649</v>
       </c>
       <c r="D10">
-        <v>4.623780478141271E-05</v>
+        <v>0.09499316662549973</v>
       </c>
       <c r="E10">
-        <v>0.0001335741690127179</v>
+        <v>0.04188175871968269</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -642,16 +633,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.006730033957574664</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.006729554835311851</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.001301928539760411</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.002461298601701856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -659,50 +650,50 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0588957704603672</v>
+        <v>0.02442495219736415</v>
       </c>
       <c r="C12">
-        <v>0.05889446288347244</v>
+        <v>0.02442220171351149</v>
       </c>
       <c r="D12">
-        <v>0.003857571631669998</v>
+        <v>0.004020011052489281</v>
       </c>
       <c r="E12">
-        <v>0.01070790458470583</v>
+        <v>0.01057404559105635</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
+      <c r="B13">
+        <v>0.09793529856350404</v>
+      </c>
+      <c r="C13">
+        <v>0.09792164994943002</v>
+      </c>
+      <c r="D13">
+        <v>0.09450215846300125</v>
+      </c>
+      <c r="E13">
+        <v>0.04105793312191963</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,16 +701,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.04882445982240158</v>
+        <v>0.006825833702830669</v>
       </c>
       <c r="C15">
-        <v>0.04883028056537969</v>
+        <v>0.006825360386177652</v>
       </c>
       <c r="D15">
-        <v>0.02063607238233089</v>
+        <v>0.001353921135887504</v>
       </c>
       <c r="E15">
-        <v>0.01070009265094995</v>
+        <v>0.002483428455889225</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -727,16 +718,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.003939139346975322</v>
+        <v>0.04891456418189106</v>
       </c>
       <c r="C16">
-        <v>0.00568355301835495</v>
+        <v>0.04892036070701301</v>
       </c>
       <c r="D16">
-        <v>0.1887047439813614</v>
+        <v>0.02050092443823814</v>
       </c>
       <c r="E16">
-        <v>0.3513489663600922</v>
+        <v>0.01071741711348295</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -744,50 +735,67 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.04891463146784954</v>
+        <v>0.3391208946704865</v>
       </c>
       <c r="C17">
-        <v>0.04892042799286241</v>
+        <v>0.3391208946704865</v>
       </c>
       <c r="D17">
-        <v>0.02050092443823814</v>
+        <v>0.02696777693927288</v>
       </c>
       <c r="E17">
-        <v>0.01071741711348295</v>
+        <v>0.04311384260654449</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.0007623236160725355</v>
-      </c>
-      <c r="C18">
-        <v>0.0007623238489031792</v>
-      </c>
-      <c r="D18">
-        <v>4.537929999059997E-05</v>
-      </c>
-      <c r="E18">
-        <v>0.0001242232538061216</v>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0.3391208946704865</v>
-      </c>
-      <c r="C19">
-        <v>0.3391208946704865</v>
-      </c>
-      <c r="D19">
-        <v>0.02696777693927288</v>
-      </c>
-      <c r="E19">
-        <v>0.04311384260654449</v>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.04882439286961621</v>
+      </c>
+      <c r="C20">
+        <v>0.04883021361261736</v>
+      </c>
+      <c r="D20">
+        <v>0.02063607238233089</v>
+      </c>
+      <c r="E20">
+        <v>0.01070009265094995</v>
       </c>
     </row>
   </sheetData>
